--- a/data/trans_orig/IP1015-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Clase-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93496</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198088</t>
+          <t>198037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198543</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>399007</t>
+          <t>398592</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123201</t>
+          <t>123782</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227875</t>
+          <t>227897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5586</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5622</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679017</t>
+          <t>679074</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317905</t>
+          <t>1317837</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322786</t>
+          <t>1322787</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83128</t>
+          <t>82399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167205</t>
+          <t>167231</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202725</t>
+          <t>202356</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>430373</t>
+          <t>429860</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4462</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4122</t>
+          <t>3453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135372</t>
+          <t>136347</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284881</t>
+          <t>285550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5230,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>71099</t>
+          <t>70983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124494</t>
+          <t>124876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>611</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>671693</t>
+          <t>671470</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>708086</t>
+          <t>707521</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>713501</t>
+          <t>712890</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381334</t>
+          <t>1381371</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386975</t>
+          <t>1386835</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207640</t>
+          <t>207604</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431180</t>
+          <t>431512</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>140161</t>
+          <t>139862</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274968</t>
+          <t>275692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>704915</t>
+          <t>705501</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376536</t>
+          <t>1376218</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/IP1015-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,107 +722,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4016</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96872</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93506</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96872</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>94164</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>198037</t>
+          <t>197882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3790</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4215</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1869,67 +1869,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>201374</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>198537</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>201374</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>198595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398592</t>
+          <t>399017</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126589</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>124147</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126589</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123782</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227897</t>
+          <t>228183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,84 +2780,84 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>669</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5529</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
           <t>672</t>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>5769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>682529</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>679004</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683934</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>682529</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>679074</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>683930</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1317837</t>
+          <t>1317690</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3813,47 +3813,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,107 +4043,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4491</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3864</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86143</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83823</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,47%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86143</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>82399</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167231</t>
+          <t>167343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,107 +4386,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2542</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>2412</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205148</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202356</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>203086</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,77%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>619</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429860</t>
+          <t>430080</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,107 +4729,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3487</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3453</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>136393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,54%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>136347</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285550</t>
+          <t>285522</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,107 +5072,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3055</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3073</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>73431</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>70709</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>73431</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>70983</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124876</t>
+          <t>125420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5637</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2897</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>611</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6211</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>711460</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>707864</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>712896</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,21%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>972</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>673601</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>671470</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>671184</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>711460</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>707521</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>712890</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1987</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1381371</t>
+          <t>1381456</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386835</t>
+          <t>1386893</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6105,47 +6105,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6448,47 +6448,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,107 +7021,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3250</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2919</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210208</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207303</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210208</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>207604</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431512</t>
+          <t>431171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,107 +7364,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>718</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3226</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4820</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3590</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>142370</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>139457</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>142370</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>139862</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>275692</t>
+          <t>274462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7820,47 +7820,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,107 +8050,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>4236</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4786</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5021</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>708373</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>705572</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,41%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>708373</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>705501</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1376218</t>
+          <t>1376453</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
